--- a/static/demo/assess/case_76.xlsx
+++ b/static/demo/assess/case_76.xlsx
@@ -3864,7 +3864,7 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Credits of ₹10,000 or more of which at least 80% was debited within 2 days.</t>
+          <t>Credits of ₹10,000 or more matched by at least 80% of their value in debits within 2 days; each debit is counted against one credit only. A timing pattern, not money traced.</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>Credits of ₹10,000 or more of which at least 80% was debited within 2 days.</t>
+          <t>Credits of ₹10,000 or more matched by at least 80% of their value in debits within 2 days; each debit is counted against one credit only. A timing pattern, not money traced.</t>
         </is>
       </c>
     </row>

--- a/static/demo/assess/case_76.xlsx
+++ b/static/demo/assess/case_76.xlsx
@@ -3856,7 +3856,7 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Large credits moved out within 2 days (share)</t>
+          <t>Credits matched by subsequent debits within 2 days (share of large credits)</t>
         </is>
       </c>
       <c r="B31" s="9" t="n">
@@ -4564,7 +4564,7 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>Large credits moved out within 2 days (share)</t>
+          <t>Credits matched by subsequent debits within 2 days (share of large credits)</t>
         </is>
       </c>
       <c r="B65" s="9" t="n">
